--- a/diseases/d236/2015-2019.xlsx
+++ b/diseases/d236/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>66</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>19.94249912751566</v>
       </c>
@@ -1410,9 +1407,6 @@
       <c r="O5" t="n">
         <v>138</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>2.659076864855887</v>
       </c>
@@ -1806,9 +1800,6 @@
       <c r="O7" t="n">
         <v>151</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>2.909569612994485</v>
       </c>
@@ -2202,9 +2193,6 @@
       <c r="O9" t="n">
         <v>158</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>3.044450323530653</v>
       </c>
@@ -2598,9 +2586,6 @@
       <c r="O11" t="n">
         <v>153</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>2.948106958861962</v>
       </c>
@@ -2994,9 +2979,6 @@
       <c r="O13" t="n">
         <v>148</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>2.85176359419327</v>
       </c>
@@ -3390,9 +3372,6 @@
       <c r="O15" t="n">
         <v>174</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>3.352749090470466</v>
       </c>
@@ -3786,9 +3765,6 @@
       <c r="O17" t="n">
         <v>155</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>2.986644304729438</v>
       </c>
@@ -4182,9 +4158,6 @@
       <c r="O19" t="n">
         <v>205</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>3.950077951416354</v>
       </c>
@@ -4578,9 +4551,6 @@
       <c r="O21" t="n">
         <v>248</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>4.7786308875671</v>
       </c>
@@ -4974,9 +4944,6 @@
       <c r="O23" t="n">
         <v>234</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>4.508869466494764</v>
       </c>
@@ -5370,9 +5337,6 @@
       <c r="O25" t="n">
         <v>240</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>4.624481504097194</v>
       </c>
@@ -5766,9 +5730,6 @@
       <c r="O27" t="n">
         <v>228</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>4.393257428892335</v>
       </c>
@@ -6162,9 +6123,6 @@
       <c r="O29" t="n">
         <v>93</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>27.71374974483981</v>
       </c>
@@ -6807,9 +6765,6 @@
       <c r="O32" t="n">
         <v>250</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>4.774652629697232</v>
       </c>
@@ -7203,9 +7158,6 @@
       <c r="O34" t="n">
         <v>413</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>4.161930329487831</v>
       </c>
@@ -7599,9 +7551,6 @@
       <c r="O36" t="n">
         <v>230</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>4.392680419321453</v>
       </c>
@@ -7995,9 +7944,6 @@
       <c r="O38" t="n">
         <v>465</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>4.685950613103731</v>
       </c>
@@ -8391,9 +8337,6 @@
       <c r="O40" t="n">
         <v>194</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>3.705130440645052</v>
       </c>
@@ -8787,9 +8730,6 @@
       <c r="O42" t="n">
         <v>404</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>4.071234511169694</v>
       </c>
@@ -9183,9 +9123,6 @@
       <c r="O44" t="n">
         <v>160</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>3.055777683006228</v>
       </c>
@@ -9579,9 +9516,6 @@
       <c r="O46" t="n">
         <v>372</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>3.748760490482986</v>
       </c>
@@ -9975,9 +9909,6 @@
       <c r="O48" t="n">
         <v>175</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>3.342256840788063</v>
       </c>
@@ -10371,9 +10302,6 @@
       <c r="O50" t="n">
         <v>354</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>3.567368853846712</v>
       </c>
@@ -10767,9 +10695,6 @@
       <c r="O52" t="n">
         <v>206</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>3.934313766870519</v>
       </c>
@@ -11163,9 +11088,6 @@
       <c r="O54" t="n">
         <v>329</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>3.315436025185221</v>
       </c>
@@ -11559,9 +11481,6 @@
       <c r="O56" t="n">
         <v>203</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>3.877017935314152</v>
       </c>
@@ -11955,9 +11874,6 @@
       <c r="O58" t="n">
         <v>335</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>3.375899904063979</v>
       </c>
@@ -12351,9 +12267,6 @@
       <c r="O60" t="n">
         <v>259</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>4.946540124366332</v>
       </c>
@@ -12747,9 +12660,6 @@
       <c r="O62" t="n">
         <v>382</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>3.849533621947582</v>
       </c>
@@ -13143,9 +13053,6 @@
       <c r="O64" t="n">
         <v>265</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>5.061131787479066</v>
       </c>
@@ -13539,9 +13446,6 @@
       <c r="O66" t="n">
         <v>376</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>3.789069743068824</v>
       </c>
@@ -13935,9 +13839,6 @@
       <c r="O68" t="n">
         <v>216</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>4.125299872058408</v>
       </c>
@@ -14331,9 +14232,6 @@
       <c r="O70" t="n">
         <v>315</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>3.174353641134786</v>
       </c>
@@ -14727,9 +14625,6 @@
       <c r="O72" t="n">
         <v>209</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>3.991609598426885</v>
       </c>
@@ -15123,9 +15018,6 @@
       <c r="O74" t="n">
         <v>311</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>3.134044388548948</v>
       </c>
@@ -15519,9 +15411,6 @@
       <c r="O76" t="n">
         <v>166</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>3.170369346118962</v>
       </c>
@@ -15915,9 +15804,6 @@
       <c r="O78" t="n">
         <v>335</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>3.375899904063979</v>
       </c>
@@ -16311,9 +16197,6 @@
       <c r="O80" t="n">
         <v>69</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>20.0854943433135</v>
       </c>
@@ -16956,9 +16839,6 @@
       <c r="O83" t="n">
         <v>251</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>4.756668455944675</v>
       </c>
@@ -17352,9 +17232,6 @@
       <c r="O85" t="n">
         <v>326</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>3.241245666387433</v>
       </c>
@@ -17748,9 +17625,6 @@
       <c r="O87" t="n">
         <v>209</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>3.960731901563494</v>
       </c>
@@ -18144,9 +18018,6 @@
       <c r="O89" t="n">
         <v>293</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>2.913144111200975</v>
       </c>
@@ -18540,9 +18411,6 @@
       <c r="O91" t="n">
         <v>214</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>4.055486253275539</v>
       </c>
@@ -18936,9 +18804,6 @@
       <c r="O93" t="n">
         <v>350</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>3.479864979250311</v>
       </c>
@@ -19332,9 +19197,6 @@
       <c r="O95" t="n">
         <v>183</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>3.468009272660858</v>
       </c>
@@ -19728,9 +19590,6 @@
       <c r="O97" t="n">
         <v>270</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>2.684467269707382</v>
       </c>
@@ -20124,9 +19983,6 @@
       <c r="O99" t="n">
         <v>189</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>3.581714494715313</v>
       </c>
@@ -20520,9 +20376,6 @@
       <c r="O101" t="n">
         <v>296</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>2.942971525308834</v>
       </c>
@@ -20916,9 +20769,6 @@
       <c r="O103" t="n">
         <v>226</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>4.282896697384449</v>
       </c>
@@ -21312,9 +21162,6 @@
       <c r="O105" t="n">
         <v>276</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>2.744122097923102</v>
       </c>
@@ -21708,9 +21555,6 @@
       <c r="O107" t="n">
         <v>201</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>3.809124938824222</v>
       </c>
@@ -22104,9 +21948,6 @@
       <c r="O109" t="n">
         <v>272</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>2.704352212445956</v>
       </c>
@@ -22500,9 +22341,6 @@
       <c r="O111" t="n">
         <v>230</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>4.358700178754085</v>
       </c>
@@ -22896,9 +22734,6 @@
       <c r="O113" t="n">
         <v>344</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>3.420210151034591</v>
       </c>
@@ -23292,9 +23127,6 @@
       <c r="O115" t="n">
         <v>255</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>4.832471937314311</v>
       </c>
@@ -23688,9 +23520,6 @@
       <c r="O117" t="n">
         <v>335</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>3.330727908711012</v>
       </c>
@@ -24084,9 +23913,6 @@
       <c r="O119" t="n">
         <v>217</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>4.112338864302767</v>
       </c>
@@ -24480,9 +24306,6 @@
       <c r="O121" t="n">
         <v>338</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>3.360555322818872</v>
       </c>
@@ -24876,9 +24699,6 @@
       <c r="O123" t="n">
         <v>223</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>4.226044086357221</v>
       </c>
@@ -25272,9 +25092,6 @@
       <c r="O125" t="n">
         <v>325</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>3.231303195018146</v>
       </c>
@@ -25668,9 +25485,6 @@
       <c r="O127" t="n">
         <v>171</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>3.24059882855195</v>
       </c>
@@ -26064,9 +25878,6 @@
       <c r="O129" t="n">
         <v>296</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>2.942971525308834</v>
       </c>
@@ -26460,9 +26271,6 @@
       <c r="O131" t="n">
         <v>78</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>22.10546004863201</v>
       </c>
@@ -27105,9 +26913,6 @@
       <c r="O134" t="n">
         <v>230</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>4.33002102413469</v>
       </c>
@@ -27501,9 +27306,6 @@
       <c r="O136" t="n">
         <v>330</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>3.243114315504607</v>
       </c>
@@ -27897,9 +27699,6 @@
       <c r="O138" t="n">
         <v>192</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>3.614626246234176</v>
       </c>
@@ -28293,9 +28092,6 @@
       <c r="O140" t="n">
         <v>265</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>2.604319071541579</v>
       </c>
@@ -28689,9 +28485,6 @@
       <c r="O142" t="n">
         <v>158</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>2.974536181796874</v>
       </c>
@@ -29085,9 +28878,6 @@
       <c r="O144" t="n">
         <v>331</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>3.2529419346425</v>
       </c>
@@ -29481,9 +29271,6 @@
       <c r="O146" t="n">
         <v>187</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>3.520495354405161</v>
       </c>
@@ -29877,9 +29664,6 @@
       <c r="O148" t="n">
         <v>280</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>2.751733358609969</v>
       </c>
@@ -30273,9 +30057,6 @@
       <c r="O150" t="n">
         <v>169</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>3.181624143820707</v>
       </c>
@@ -30669,9 +30450,6 @@
       <c r="O152" t="n">
         <v>265</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>2.604319071541579</v>
       </c>
@@ -31065,9 +30843,6 @@
       <c r="O154" t="n">
         <v>253</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>4.763023126548159</v>
       </c>
@@ -31461,9 +31236,6 @@
       <c r="O156" t="n">
         <v>301</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>2.958113360505717</v>
       </c>
@@ -31857,9 +31629,6 @@
       <c r="O158" t="n">
         <v>219</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>4.122933062110857</v>
       </c>
@@ -32253,9 +32022,6 @@
       <c r="O160" t="n">
         <v>314</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>3.085872409298323</v>
       </c>
@@ -32649,9 +32415,6 @@
       <c r="O162" t="n">
         <v>284</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>5.346634655888052</v>
       </c>
@@ -33045,9 +32808,6 @@
       <c r="O164" t="n">
         <v>400</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>3.9310476551571</v>
       </c>
@@ -33441,9 +33201,6 @@
       <c r="O166" t="n">
         <v>243</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>4.574761342890129</v>
       </c>
@@ -33837,9 +33594,6 @@
       <c r="O168" t="n">
         <v>365</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>3.587080985330853</v>
       </c>
@@ -34233,9 +33987,6 @@
       <c r="O170" t="n">
         <v>241</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>4.537108986158523</v>
       </c>
@@ -34629,9 +34380,6 @@
       <c r="O172" t="n">
         <v>369</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>3.626391461882424</v>
       </c>
@@ -35025,9 +34773,6 @@
       <c r="O174" t="n">
         <v>203</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>3.82171420825801</v>
       </c>
@@ -35421,9 +35166,6 @@
       <c r="O176" t="n">
         <v>372</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>3.655874319296103</v>
       </c>
@@ -35817,9 +35559,6 @@
       <c r="O178" t="n">
         <v>188</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>3.539321532770964</v>
       </c>
@@ -36213,9 +35952,6 @@
       <c r="O180" t="n">
         <v>264</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>2.594491452403686</v>
       </c>
@@ -36609,9 +36345,6 @@
       <c r="O182" t="n">
         <v>97</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>26.89219142249989</v>
       </c>
@@ -37254,9 +36987,6 @@
       <c r="O185" t="n">
         <v>217</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>4.057796106217395</v>
       </c>
@@ -37650,9 +37380,6 @@
       <c r="O187" t="n">
         <v>314</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>3.054734717205988</v>
       </c>
@@ -38046,9 +37773,6 @@
       <c r="O189" t="n">
         <v>182</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>3.403312863279105</v>
       </c>
@@ -38442,9 +38166,6 @@
       <c r="O191" t="n">
         <v>364</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>3.541157442875731</v>
       </c>
@@ -38838,9 +38559,6 @@
       <c r="O193" t="n">
         <v>195</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>3.646406639227612</v>
       </c>
@@ -39234,9 +38952,6 @@
       <c r="O195" t="n">
         <v>315</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>3.064463171719383</v>
       </c>
@@ -39630,9 +39345,6 @@
       <c r="O197" t="n">
         <v>179</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>3.34721429959868</v>
       </c>
@@ -40026,9 +39738,6 @@
       <c r="O199" t="n">
         <v>336</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>3.268760716500675</v>
       </c>
@@ -40422,9 +40131,6 @@
       <c r="O201" t="n">
         <v>193</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>3.609007596773996</v>
       </c>
@@ -40818,9 +40524,6 @@
       <c r="O203" t="n">
         <v>295</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>2.869894081451486</v>
       </c>
@@ -41214,9 +40917,6 @@
       <c r="O205" t="n">
         <v>191</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>3.57160855432038</v>
       </c>
@@ -41610,9 +41310,6 @@
       <c r="O207" t="n">
         <v>282</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>2.743424172777352</v>
       </c>
@@ -42006,9 +41703,6 @@
       <c r="O209" t="n">
         <v>187</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>3.496810469413147</v>
       </c>
@@ -42402,9 +42096,6 @@
       <c r="O211" t="n">
         <v>307</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>2.986635535612224</v>
       </c>
@@ -42798,9 +42489,6 @@
       <c r="O213" t="n">
         <v>279</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>5.217166422279507</v>
       </c>
@@ -43194,9 +42882,6 @@
       <c r="O215" t="n">
         <v>349</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>3.395230625174808</v>
       </c>
@@ -43590,9 +43275,6 @@
       <c r="O217" t="n">
         <v>228</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>4.263490839712285</v>
       </c>
@@ -43986,9 +43668,6 @@
       <c r="O219" t="n">
         <v>367</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>3.570342806415916</v>
       </c>
@@ -44382,9 +44061,6 @@
       <c r="O221" t="n">
         <v>237</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>4.431786530753559</v>
       </c>
@@ -44778,9 +44454,6 @@
       <c r="O223" t="n">
         <v>351</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>3.414687534201598</v>
       </c>
@@ -45174,9 +44847,6 @@
       <c r="O225" t="n">
         <v>227</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>4.244791318485477</v>
       </c>
@@ -45570,9 +45240,6 @@
       <c r="O227" t="n">
         <v>288</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>2.801794899857721</v>
       </c>
@@ -45966,9 +45633,6 @@
       <c r="O229" t="n">
         <v>161</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>3.010622917516131</v>
       </c>
@@ -46361,9 +46025,6 @@
       </c>
       <c r="O231" t="n">
         <v>288</v>
-      </c>
-      <c r="Q231" t="n">
-        <v>0</v>
       </c>
       <c r="R231" t="n">
         <v>2.801794899857721</v>
